--- a/tmp/dailyReport.xlsx
+++ b/tmp/dailyReport.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28FFD349-6AA6-46DF-AD6D-11BCAFCC8CF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C751E1CC-9F63-45A4-A013-E7A207BC3AD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10500" yWindow="684" windowWidth="11820" windowHeight="11292" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>Service Type</t>
   </si>
@@ -64,6 +64,15 @@
   </si>
   <si>
     <t>Operator Name</t>
+  </si>
+  <si>
+    <t>Frequency</t>
+  </si>
+  <si>
+    <t>Scope</t>
+  </si>
+  <si>
+    <t>Calibration</t>
   </si>
 </sst>
 </file>
@@ -225,6 +234,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -242,9 +254,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -274,7 +283,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>847725</xdr:colOff>
+      <xdr:colOff>984885</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>1190625</xdr:rowOff>
     </xdr:to>
@@ -640,50 +649,56 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:M6"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.85546875" style="2" customWidth="1"/>
-    <col min="2" max="2" width="11.7109375" style="2" customWidth="1"/>
-    <col min="3" max="3" width="21" style="13" customWidth="1"/>
-    <col min="4" max="4" width="23" style="3" customWidth="1"/>
-    <col min="5" max="5" width="19.85546875" style="2" customWidth="1"/>
-    <col min="6" max="6" width="14.7109375" style="2" customWidth="1"/>
-    <col min="7" max="7" width="21.85546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18" style="2" customWidth="1"/>
-    <col min="9" max="9" width="12" style="2" customWidth="1"/>
-    <col min="10" max="10" width="11.7109375" style="6" customWidth="1"/>
+    <col min="1" max="1" width="14.88671875" style="2" customWidth="1"/>
+    <col min="2" max="2" width="11.6640625" style="2" customWidth="1"/>
+    <col min="3" max="4" width="21" style="7" customWidth="1"/>
+    <col min="5" max="7" width="23" style="3" customWidth="1"/>
+    <col min="8" max="8" width="19.88671875" style="2" customWidth="1"/>
+    <col min="9" max="9" width="14.6640625" style="2" customWidth="1"/>
+    <col min="10" max="10" width="21.88671875" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="18" style="2" customWidth="1"/>
+    <col min="12" max="12" width="12" style="2" customWidth="1"/>
+    <col min="13" max="13" width="11.6640625" style="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="99" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="7" t="s">
+    <row r="1" spans="1:13" ht="99" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
-      <c r="F1" s="8"/>
-      <c r="G1" s="8"/>
-      <c r="H1" s="8"/>
-      <c r="I1" s="8"/>
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="9"/>
+      <c r="I1" s="9"/>
       <c r="J1" s="9"/>
+      <c r="K1" s="9"/>
+      <c r="L1" s="9"/>
+      <c r="M1" s="10"/>
     </row>
-    <row r="2" spans="1:10" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="10" t="s">
+    <row r="2" spans="1:13" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="11"/>
-      <c r="C2" s="11"/>
-      <c r="D2" s="11"/>
-      <c r="E2" s="11"/>
-      <c r="F2" s="11"/>
-      <c r="G2" s="11"/>
-      <c r="H2" s="11"/>
-      <c r="I2" s="11"/>
+      <c r="B2" s="12"/>
+      <c r="C2" s="12"/>
+      <c r="D2" s="12"/>
+      <c r="E2" s="12"/>
+      <c r="F2" s="12"/>
+      <c r="G2" s="12"/>
+      <c r="H2" s="12"/>
+      <c r="I2" s="12"/>
       <c r="J2" s="12"/>
+      <c r="K2" s="12"/>
+      <c r="L2" s="12"/>
+      <c r="M2" s="13"/>
     </row>
-    <row r="3" spans="1:10" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>0</v>
       </c>
@@ -694,40 +709,49 @@
         <v>9</v>
       </c>
       <c r="D3" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="F3" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="H3" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="I3" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="J3" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="K3" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="I3" s="4" t="s">
+      <c r="L3" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="J3" s="4" t="s">
+      <c r="M3" s="4" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="E4" s="3"/>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="H4" s="3"/>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="E5" s="3"/>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="H5" s="3"/>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="E6" s="3"/>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="H6" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="A2:M2"/>
   </mergeCells>
   <pageMargins left="0.11811023622047245" right="0.11811023622047245" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup orientation="landscape" horizontalDpi="4294967295" verticalDpi="4294967295" r:id="rId1"/>

--- a/tmp/dailyReport.xlsx
+++ b/tmp/dailyReport.xlsx
@@ -1,85 +1,83 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C751E1CC-9F63-45A4-A013-E7A207BC3AD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F184C8D7-1D83-47C1-84D7-A3F4299FD19B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10500" yWindow="684" windowWidth="11820" windowHeight="11292" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Regular service" sheetId="1" r:id="rId1"/>
+    <sheet name="Unscheduled-Work" sheetId="3" r:id="rId2"/>
+    <sheet name="Complaints" sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="152511"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
-  <si>
-    <t>Service Type</t>
-  </si>
-  <si>
-    <t>Image 1</t>
-  </si>
-  <si>
-    <t>Image 2</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="18">
   <si>
     <t>Contact No:      Email: natco.epcorn@gmail.com / sales@epcorn.com</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">                                                                   </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="26"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Daily Service Report</t>
-    </r>
-  </si>
-  <si>
-    <t>Time</t>
-  </si>
-  <si>
     <t>Service Name</t>
   </si>
   <si>
-    <t>Service Action</t>
+    <t>Location</t>
+  </si>
+  <si>
+    <t>Frequency</t>
+  </si>
+  <si>
+    <t>Scope</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>Serviced By</t>
+  </si>
+  <si>
+    <t>Daily Service Report</t>
+  </si>
+  <si>
+    <t>Complaint Number</t>
+  </si>
+  <si>
+    <t>Services</t>
+  </si>
+  <si>
+    <t>Assigned to</t>
+  </si>
+  <si>
+    <t>Comment</t>
   </si>
   <si>
     <t>Status</t>
   </si>
   <si>
-    <t>Location</t>
-  </si>
-  <si>
-    <t>Operator Comment</t>
-  </si>
-  <si>
-    <t>Operator Name</t>
-  </si>
-  <si>
-    <t>Frequency</t>
-  </si>
-  <si>
-    <t>Scope</t>
-  </si>
-  <si>
-    <t>Calibration</t>
+    <t>Reopen Count</t>
+  </si>
+  <si>
+    <t>Raised By</t>
+  </si>
+  <si>
+    <t>Approved By</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Create Date </t>
+  </si>
+  <si>
+    <t>Completed Date</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -127,6 +125,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -142,7 +147,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -171,15 +176,6 @@
       </left>
       <right/>
       <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
@@ -195,11 +191,22 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
       <bottom/>
       <diagonal/>
     </border>
@@ -208,17 +215,41 @@
       <right style="thin">
         <color indexed="64"/>
       </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
       <top/>
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -230,30 +261,51 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -276,16 +328,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>190500</xdr:colOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>104775</xdr:rowOff>
+      <xdr:rowOff>68580</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>984885</xdr:colOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>3301365</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>1190625</xdr:rowOff>
+      <xdr:rowOff>1257299</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -314,8 +366,118 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1181100" y="104775"/>
-          <a:ext cx="4371975" cy="1085850"/>
+          <a:off x="7993380" y="68580"/>
+          <a:ext cx="3301365" cy="1188719"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>1181099</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>15240</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>952500</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>988679</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{92EF3CF8-98B5-4A46-9BAB-8167DA9A89E6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8191499" y="15240"/>
+          <a:ext cx="1805941" cy="973439"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>1232746</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{44A679A4-AD70-4E08-8817-CAC61DD50EFE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6979920" y="0"/>
+          <a:ext cx="2948940" cy="1232746"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -649,112 +811,572 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.88671875" style="2" customWidth="1"/>
-    <col min="2" max="2" width="11.6640625" style="2" customWidth="1"/>
-    <col min="3" max="4" width="21" style="7" customWidth="1"/>
-    <col min="5" max="7" width="23" style="3" customWidth="1"/>
-    <col min="8" max="8" width="19.88671875" style="2" customWidth="1"/>
-    <col min="9" max="9" width="14.6640625" style="2" customWidth="1"/>
-    <col min="10" max="10" width="21.88671875" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="18" style="2" customWidth="1"/>
-    <col min="12" max="12" width="12" style="2" customWidth="1"/>
-    <col min="13" max="13" width="11.6640625" style="6" customWidth="1"/>
+    <col min="1" max="1" width="14.88671875" style="7" customWidth="1"/>
+    <col min="2" max="2" width="19.44140625" style="7" customWidth="1"/>
+    <col min="3" max="3" width="24.109375" style="8" customWidth="1"/>
+    <col min="4" max="4" width="35.109375" style="8" customWidth="1"/>
+    <col min="5" max="5" width="23" style="9" customWidth="1"/>
+    <col min="6" max="6" width="48.88671875" style="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="99" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="8" t="s">
+    <row r="1" spans="1:6" ht="99" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="18"/>
+    </row>
+    <row r="2" spans="1:6" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="19" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="20"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="21"/>
+    </row>
+    <row r="3" spans="1:6" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A3" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="F3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
-      <c r="H1" s="9"/>
-      <c r="I1" s="9"/>
-      <c r="J1" s="9"/>
-      <c r="K1" s="9"/>
-      <c r="L1" s="9"/>
-      <c r="M1" s="10"/>
-    </row>
-    <row r="2" spans="1:13" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="12"/>
-      <c r="C2" s="12"/>
-      <c r="D2" s="12"/>
-      <c r="E2" s="12"/>
-      <c r="F2" s="12"/>
-      <c r="G2" s="12"/>
-      <c r="H2" s="12"/>
-      <c r="I2" s="12"/>
-      <c r="J2" s="12"/>
-      <c r="K2" s="12"/>
-      <c r="L2" s="12"/>
-      <c r="M2" s="13"/>
-    </row>
-    <row r="3" spans="1:13" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A3" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="H3" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="I3" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="J3" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="K3" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="L3" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="M3" s="4" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="H4" s="3"/>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="H5" s="3"/>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="H6" s="3"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" s="2"/>
+      <c r="B4" s="2"/>
+      <c r="C4" s="5"/>
+      <c r="D4" s="5"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" s="2"/>
+      <c r="B5" s="2"/>
+      <c r="C5" s="5"/>
+      <c r="D5" s="5"/>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" s="2"/>
+      <c r="B6" s="2"/>
+      <c r="C6" s="5"/>
+      <c r="D6" s="5"/>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7" s="2"/>
+      <c r="B7" s="2"/>
+      <c r="C7" s="5"/>
+      <c r="D7" s="5"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8" s="2"/>
+      <c r="B8" s="2"/>
+      <c r="C8" s="5"/>
+      <c r="D8" s="5"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A9" s="2"/>
+      <c r="B9" s="2"/>
+      <c r="C9" s="5"/>
+      <c r="D9" s="5"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10" s="2"/>
+      <c r="B10" s="2"/>
+      <c r="C10" s="5"/>
+      <c r="D10" s="5"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11" s="2"/>
+      <c r="B11" s="2"/>
+      <c r="C11" s="5"/>
+      <c r="D11" s="5"/>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A12" s="2"/>
+      <c r="B12" s="2"/>
+      <c r="C12" s="5"/>
+      <c r="D12" s="5"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A13" s="2"/>
+      <c r="B13" s="2"/>
+      <c r="C13" s="5"/>
+      <c r="D13" s="5"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A14" s="2"/>
+      <c r="B14" s="2"/>
+      <c r="C14" s="5"/>
+      <c r="D14" s="5"/>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:M1"/>
-    <mergeCell ref="A2:M2"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:F2"/>
   </mergeCells>
   <pageMargins left="0.11811023622047245" right="0.11811023622047245" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup orientation="landscape" horizontalDpi="4294967295" verticalDpi="4294967295" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95137C80-9D41-4A1F-AAF8-29130318C828}">
+  <dimension ref="A1:H14"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="19.77734375" customWidth="1"/>
+    <col min="2" max="2" width="20.33203125" customWidth="1"/>
+    <col min="3" max="3" width="28" customWidth="1"/>
+    <col min="4" max="4" width="20.44140625" customWidth="1"/>
+    <col min="5" max="5" width="13.6640625" customWidth="1"/>
+    <col min="6" max="6" width="17.21875" customWidth="1"/>
+    <col min="7" max="7" width="12.44140625" customWidth="1"/>
+    <col min="8" max="8" width="14.77734375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="80.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="22"/>
+      <c r="H1" s="22"/>
+    </row>
+    <row r="2" spans="1:8" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="15"/>
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="15"/>
+      <c r="G2" s="15"/>
+      <c r="H2" s="15"/>
+    </row>
+    <row r="3" spans="1:8" s="12" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A3" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="E3" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="G3" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="H3" s="11" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A4" s="10"/>
+      <c r="B4" s="10"/>
+      <c r="C4" s="10"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="10"/>
+      <c r="F4" s="10"/>
+      <c r="G4" s="10"/>
+      <c r="H4" s="10"/>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A5" s="10"/>
+      <c r="B5" s="10"/>
+      <c r="C5" s="10"/>
+      <c r="D5" s="10"/>
+      <c r="E5" s="10"/>
+      <c r="F5" s="10"/>
+      <c r="G5" s="10"/>
+      <c r="H5" s="10"/>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A6" s="10"/>
+      <c r="B6" s="10"/>
+      <c r="C6" s="10"/>
+      <c r="D6" s="10"/>
+      <c r="E6" s="10"/>
+      <c r="F6" s="10"/>
+      <c r="G6" s="10"/>
+      <c r="H6" s="10"/>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A7" s="10"/>
+      <c r="B7" s="10"/>
+      <c r="C7" s="10"/>
+      <c r="D7" s="10"/>
+      <c r="E7" s="10"/>
+      <c r="F7" s="10"/>
+      <c r="G7" s="10"/>
+      <c r="H7" s="10"/>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A8" s="10"/>
+      <c r="B8" s="10"/>
+      <c r="C8" s="10"/>
+      <c r="D8" s="10"/>
+      <c r="E8" s="10"/>
+      <c r="F8" s="10"/>
+      <c r="G8" s="10"/>
+      <c r="H8" s="10"/>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A9" s="10"/>
+      <c r="B9" s="10"/>
+      <c r="C9" s="10"/>
+      <c r="D9" s="10"/>
+      <c r="E9" s="10"/>
+      <c r="F9" s="10"/>
+      <c r="G9" s="10"/>
+      <c r="H9" s="10"/>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A10" s="10"/>
+      <c r="B10" s="10"/>
+      <c r="C10" s="10"/>
+      <c r="D10" s="10"/>
+      <c r="E10" s="10"/>
+      <c r="F10" s="10"/>
+      <c r="G10" s="10"/>
+      <c r="H10" s="10"/>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A11" s="10"/>
+      <c r="B11" s="10"/>
+      <c r="C11" s="10"/>
+      <c r="D11" s="10"/>
+      <c r="E11" s="10"/>
+      <c r="F11" s="10"/>
+      <c r="G11" s="10"/>
+      <c r="H11" s="10"/>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A12" s="10"/>
+      <c r="B12" s="10"/>
+      <c r="C12" s="10"/>
+      <c r="D12" s="10"/>
+      <c r="E12" s="10"/>
+      <c r="F12" s="10"/>
+      <c r="G12" s="10"/>
+      <c r="H12" s="10"/>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A13" s="10"/>
+      <c r="B13" s="10"/>
+      <c r="C13" s="10"/>
+      <c r="D13" s="10"/>
+      <c r="E13" s="10"/>
+      <c r="F13" s="10"/>
+      <c r="G13" s="10"/>
+      <c r="H13" s="10"/>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A14" s="10"/>
+      <c r="B14" s="10"/>
+      <c r="C14" s="10"/>
+      <c r="D14" s="10"/>
+      <c r="E14" s="10"/>
+      <c r="F14" s="10"/>
+      <c r="G14" s="10"/>
+      <c r="H14" s="10"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:H2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B01D6A6B-C461-47EF-B4E7-783194B4D6F8}">
+  <dimension ref="A1:H19"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="20.44140625" customWidth="1"/>
+    <col min="2" max="2" width="19" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.88671875" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+    <col min="5" max="5" width="26.44140625" customWidth="1"/>
+    <col min="6" max="6" width="19.44140625" customWidth="1"/>
+    <col min="7" max="7" width="9.109375" customWidth="1"/>
+    <col min="8" max="8" width="14.44140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="99" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
+      <c r="H1" s="14"/>
+    </row>
+    <row r="2" spans="1:8" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="15"/>
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="15"/>
+      <c r="G2" s="15"/>
+      <c r="H2" s="15"/>
+    </row>
+    <row r="3" spans="1:8" s="13" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A3" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G3" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="H3" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A4" s="10"/>
+      <c r="B4" s="10"/>
+      <c r="C4" s="10"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="10"/>
+      <c r="F4" s="10"/>
+      <c r="G4" s="10"/>
+      <c r="H4" s="10"/>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A5" s="10"/>
+      <c r="B5" s="10"/>
+      <c r="C5" s="10"/>
+      <c r="D5" s="10"/>
+      <c r="E5" s="10"/>
+      <c r="F5" s="10"/>
+      <c r="G5" s="10"/>
+      <c r="H5" s="10"/>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A6" s="10"/>
+      <c r="B6" s="10"/>
+      <c r="C6" s="10"/>
+      <c r="D6" s="10"/>
+      <c r="E6" s="10"/>
+      <c r="F6" s="10"/>
+      <c r="G6" s="10"/>
+      <c r="H6" s="10"/>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A7" s="10"/>
+      <c r="B7" s="10"/>
+      <c r="C7" s="10"/>
+      <c r="D7" s="10"/>
+      <c r="E7" s="10"/>
+      <c r="F7" s="10"/>
+      <c r="G7" s="10"/>
+      <c r="H7" s="10"/>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A8" s="10"/>
+      <c r="B8" s="10"/>
+      <c r="C8" s="10"/>
+      <c r="D8" s="10"/>
+      <c r="E8" s="10"/>
+      <c r="F8" s="10"/>
+      <c r="G8" s="10"/>
+      <c r="H8" s="10"/>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A9" s="10"/>
+      <c r="B9" s="10"/>
+      <c r="C9" s="10"/>
+      <c r="D9" s="10"/>
+      <c r="E9" s="10"/>
+      <c r="F9" s="10"/>
+      <c r="G9" s="10"/>
+      <c r="H9" s="10"/>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A10" s="10"/>
+      <c r="B10" s="10"/>
+      <c r="C10" s="10"/>
+      <c r="D10" s="10"/>
+      <c r="E10" s="10"/>
+      <c r="F10" s="10"/>
+      <c r="G10" s="10"/>
+      <c r="H10" s="10"/>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A11" s="10"/>
+      <c r="B11" s="10"/>
+      <c r="C11" s="10"/>
+      <c r="D11" s="10"/>
+      <c r="E11" s="10"/>
+      <c r="F11" s="10"/>
+      <c r="G11" s="10"/>
+      <c r="H11" s="10"/>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A12" s="10"/>
+      <c r="B12" s="10"/>
+      <c r="C12" s="10"/>
+      <c r="D12" s="10"/>
+      <c r="E12" s="10"/>
+      <c r="F12" s="10"/>
+      <c r="G12" s="10"/>
+      <c r="H12" s="10"/>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A13" s="10"/>
+      <c r="B13" s="10"/>
+      <c r="C13" s="10"/>
+      <c r="D13" s="10"/>
+      <c r="E13" s="10"/>
+      <c r="F13" s="10"/>
+      <c r="G13" s="10"/>
+      <c r="H13" s="10"/>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A14" s="10"/>
+      <c r="B14" s="10"/>
+      <c r="C14" s="10"/>
+      <c r="D14" s="10"/>
+      <c r="E14" s="10"/>
+      <c r="F14" s="10"/>
+      <c r="G14" s="10"/>
+      <c r="H14" s="10"/>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A15" s="10"/>
+      <c r="B15" s="10"/>
+      <c r="C15" s="10"/>
+      <c r="D15" s="10"/>
+      <c r="E15" s="10"/>
+      <c r="F15" s="10"/>
+      <c r="G15" s="10"/>
+      <c r="H15" s="10"/>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A16" s="10"/>
+      <c r="B16" s="10"/>
+      <c r="C16" s="10"/>
+      <c r="D16" s="10"/>
+      <c r="E16" s="10"/>
+      <c r="F16" s="10"/>
+      <c r="G16" s="10"/>
+      <c r="H16" s="10"/>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A17" s="10"/>
+      <c r="B17" s="10"/>
+      <c r="C17" s="10"/>
+      <c r="D17" s="10"/>
+      <c r="E17" s="10"/>
+      <c r="F17" s="10"/>
+      <c r="G17" s="10"/>
+      <c r="H17" s="10"/>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A18" s="10"/>
+      <c r="B18" s="10"/>
+      <c r="C18" s="10"/>
+      <c r="D18" s="10"/>
+      <c r="E18" s="10"/>
+      <c r="F18" s="10"/>
+      <c r="G18" s="10"/>
+      <c r="H18" s="10"/>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A19" s="10"/>
+      <c r="B19" s="10"/>
+      <c r="C19" s="10"/>
+      <c r="D19" s="10"/>
+      <c r="E19" s="10"/>
+      <c r="F19" s="10"/>
+      <c r="G19" s="10"/>
+      <c r="H19" s="10"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:H2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>
--- a/tmp/dailyReport.xlsx
+++ b/tmp/dailyReport.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F184C8D7-1D83-47C1-84D7-A3F4299FD19B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F87C7795-3D6A-4B0E-99CD-D5F278811434}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Regular service" sheetId="1" r:id="rId1"/>
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="17">
   <si>
     <t>Contact No:      Email: natco.epcorn@gmail.com / sales@epcorn.com</t>
   </si>
@@ -29,9 +29,6 @@
   </si>
   <si>
     <t>Frequency</t>
-  </si>
-  <si>
-    <t>Scope</t>
   </si>
   <si>
     <t>Date</t>
@@ -147,7 +144,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -211,28 +208,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
@@ -249,7 +224,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -264,7 +239,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -292,16 +267,10 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -328,16 +297,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>929640</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>68580</xdr:rowOff>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>3301365</xdr:colOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>1602105</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>1257299</xdr:rowOff>
+      <xdr:rowOff>1188719</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -366,7 +335,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7993380" y="68580"/>
+          <a:off x="5135880" y="0"/>
           <a:ext cx="3301365" cy="1188719"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -811,46 +780,43 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.88671875" style="7" customWidth="1"/>
-    <col min="2" max="2" width="19.44140625" style="7" customWidth="1"/>
+    <col min="2" max="2" width="22.33203125" style="7" customWidth="1"/>
     <col min="3" max="3" width="24.109375" style="8" customWidth="1"/>
-    <col min="4" max="4" width="35.109375" style="8" customWidth="1"/>
-    <col min="5" max="5" width="23" style="9" customWidth="1"/>
-    <col min="6" max="6" width="48.88671875" style="9" customWidth="1"/>
+    <col min="4" max="4" width="38.33203125" style="8" customWidth="1"/>
+    <col min="5" max="5" width="31.5546875" style="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="99" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" ht="99" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="16" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B1" s="17"/>
       <c r="C1" s="17"/>
       <c r="D1" s="17"/>
       <c r="E1" s="17"/>
-      <c r="F1" s="18"/>
-    </row>
-    <row r="2" spans="1:6" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="19" t="s">
+    </row>
+    <row r="2" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="20"/>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
-      <c r="E2" s="20"/>
-      <c r="F2" s="21"/>
-    </row>
-    <row r="3" spans="1:6" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B2" s="19"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="19"/>
+    </row>
+    <row r="3" spans="1:5" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>3</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D3" s="6" t="s">
         <v>2</v>
@@ -858,102 +824,88 @@
       <c r="E3" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="F3" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="5"/>
       <c r="D4" s="5"/>
       <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="5"/>
       <c r="D5" s="5"/>
       <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="C6" s="5"/>
       <c r="D6" s="5"/>
       <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="2"/>
       <c r="B7" s="2"/>
       <c r="C7" s="5"/>
       <c r="D7" s="5"/>
       <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="5"/>
       <c r="D8" s="5"/>
       <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="5"/>
       <c r="D9" s="5"/>
       <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
       <c r="C10" s="5"/>
       <c r="D10" s="5"/>
       <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="5"/>
       <c r="D11" s="5"/>
       <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="5"/>
       <c r="D12" s="5"/>
       <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="5"/>
       <c r="D13" s="5"/>
       <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
       <c r="C14" s="5"/>
       <c r="D14" s="5"/>
       <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A2:E2"/>
   </mergeCells>
   <pageMargins left="0.11811023622047245" right="0.11811023622047245" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup orientation="landscape" horizontalDpi="4294967295" verticalDpi="4294967295" r:id="rId1"/>
@@ -977,16 +929,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="80.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="22" t="s">
-        <v>7</v>
-      </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
-      <c r="G1" s="22"/>
-      <c r="H1" s="22"/>
+      <c r="A1" s="20" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
     </row>
     <row r="2" spans="1:8" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="15" t="s">
@@ -1002,10 +954,10 @@
     </row>
     <row r="3" spans="1:8" s="12" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" s="11" t="s">
         <v>16</v>
-      </c>
-      <c r="B3" s="11" t="s">
-        <v>17</v>
       </c>
       <c r="C3" s="11" t="s">
         <v>2</v>
@@ -1014,16 +966,16 @@
         <v>1</v>
       </c>
       <c r="E3" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="F3" s="11" t="s">
-        <v>15</v>
-      </c>
       <c r="G3" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="H3" s="11" t="s">
         <v>11</v>
-      </c>
-      <c r="H3" s="11" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
@@ -1163,7 +1115,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="99" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="14" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B1" s="14"/>
       <c r="C1" s="14"/>
@@ -1187,28 +1139,28 @@
     </row>
     <row r="3" spans="1:8" s="13" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B3" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="D3" s="4" t="s">
         <v>9</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>10</v>
       </c>
       <c r="E3" s="4" t="s">
         <v>2</v>
       </c>
       <c r="F3" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G3" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="G3" s="11" t="s">
+      <c r="H3" s="11" t="s">
         <v>12</v>
-      </c>
-      <c r="H3" s="11" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
